--- a/artfynd/A 40545-2024 artfynd.xlsx
+++ b/artfynd/A 40545-2024 artfynd.xlsx
@@ -2619,10 +2619,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119869896</v>
+        <v>119869867</v>
       </c>
       <c r="B20" t="n">
-        <v>57463</v>
+        <v>97907</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2631,39 +2631,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2709,12 +2709,18 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Minst.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2733,10 +2739,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119869867</v>
+        <v>119869896</v>
       </c>
       <c r="B21" t="n">
-        <v>97907</v>
+        <v>57463</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2745,39 +2751,39 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2823,18 +2829,12 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Minst.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 40545-2024 artfynd.xlsx
+++ b/artfynd/A 40545-2024 artfynd.xlsx
@@ -2622,7 +2622,7 @@
         <v>119869867</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>119869896</v>
       </c>
       <c r="B21" t="n">
-        <v>57463</v>
+        <v>57473</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 40545-2024 artfynd.xlsx
+++ b/artfynd/A 40545-2024 artfynd.xlsx
@@ -2619,10 +2619,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119869867</v>
+        <v>119869896</v>
       </c>
       <c r="B20" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2631,39 +2631,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2709,18 +2709,12 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Minst.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2739,10 +2733,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119869896</v>
+        <v>119869867</v>
       </c>
       <c r="B21" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2751,39 +2745,39 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2829,12 +2823,18 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Minst.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 40545-2024 artfynd.xlsx
+++ b/artfynd/A 40545-2024 artfynd.xlsx
@@ -1766,7 +1766,7 @@
         <v>114666739</v>
       </c>
       <c r="B12" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>114666737</v>
       </c>
       <c r="B13" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>114666741</v>
       </c>
       <c r="B14" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>114666733</v>
       </c>
       <c r="B15" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>114666736</v>
       </c>
       <c r="B16" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>114666738</v>
       </c>
       <c r="B17" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>114666740</v>
       </c>
       <c r="B18" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>114666735</v>
       </c>
       <c r="B19" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 40545-2024 artfynd.xlsx
+++ b/artfynd/A 40545-2024 artfynd.xlsx
@@ -1766,7 +1766,7 @@
         <v>114666739</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>114666737</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>114666741</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>114666733</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>114666736</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>114666738</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>114666740</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>114666735</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 40545-2024 artfynd.xlsx
+++ b/artfynd/A 40545-2024 artfynd.xlsx
@@ -1766,7 +1766,7 @@
         <v>114666739</v>
       </c>
       <c r="B12" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>114666737</v>
       </c>
       <c r="B13" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>114666741</v>
       </c>
       <c r="B14" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>114666733</v>
       </c>
       <c r="B15" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>114666736</v>
       </c>
       <c r="B16" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>114666738</v>
       </c>
       <c r="B17" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>114666740</v>
       </c>
       <c r="B18" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>114666735</v>
       </c>
       <c r="B19" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 40545-2024 artfynd.xlsx
+++ b/artfynd/A 40545-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2851,6 +2851,123 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129684526</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57642</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100011</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Kungsörn</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Aquila chrysaetos</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Gillerfloberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>493077</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6939945</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40545-2024 artfynd.xlsx
+++ b/artfynd/A 40545-2024 artfynd.xlsx
@@ -2856,7 +2856,7 @@
         <v>129684526</v>
       </c>
       <c r="B22" t="n">
-        <v>57642</v>
+        <v>57646</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 40545-2024 artfynd.xlsx
+++ b/artfynd/A 40545-2024 artfynd.xlsx
@@ -2856,7 +2856,7 @@
         <v>129684526</v>
       </c>
       <c r="B22" t="n">
-        <v>57646</v>
+        <v>57647</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 40545-2024 artfynd.xlsx
+++ b/artfynd/A 40545-2024 artfynd.xlsx
@@ -2856,7 +2856,7 @@
         <v>129684526</v>
       </c>
       <c r="B22" t="n">
-        <v>57647</v>
+        <v>57648</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 40545-2024 artfynd.xlsx
+++ b/artfynd/A 40545-2024 artfynd.xlsx
@@ -2856,7 +2856,7 @@
         <v>129684526</v>
       </c>
       <c r="B22" t="n">
-        <v>57648</v>
+        <v>57651</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 40545-2024 artfynd.xlsx
+++ b/artfynd/A 40545-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983066</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112987238</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,6 +1004,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112982997</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1097,6 +1117,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983172</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1205,6 +1230,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112982957</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1313,6 +1343,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983153</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983190</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1522,6 +1562,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112987053</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1623,6 +1668,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112987170</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1724,6 +1774,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112987304</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1825,6 +1880,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113407078</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1926,6 +1986,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112987218</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2043,6 +2108,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129684526</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2145,6 +2215,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114666733</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2247,6 +2322,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114666735</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2349,6 +2429,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114666736</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2451,6 +2536,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114666737</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2553,6 +2643,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114666738</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2655,6 +2750,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114666739</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2757,6 +2857,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114666740</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2859,6 +2964,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114666741</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2968,6 +3078,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119869896</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3083,8 +3198,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119869867</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>